--- a/Template_Spreadsheet_Absensi_KKN.xlsx
+++ b/Template_Spreadsheet_Absensi_KKN.xlsx
@@ -54,6 +54,11 @@
           <t>Nama</t>
         </is>
       </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Password</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -64,6 +69,11 @@
       <c r="B2" t="inlineStr">
         <is>
           <t>Contoh Nama (hapus baris ini)</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t/>
         </is>
       </c>
     </row>

--- a/Template_Spreadsheet_Absensi_KKN.xlsx
+++ b/Template_Spreadsheet_Absensi_KKN.xlsx
@@ -5,6 +5,7 @@
     <sheet name="Peserta" sheetId="1" r:id="rId1"/>
     <sheet name="QR_Tokens" sheetId="2" r:id="rId2"/>
     <sheet name="Absensi" sheetId="3" r:id="rId3"/>
+    <sheet name="Laporan" sheetId="4" r:id="rId5"/>
   </sheets>
 </workbook>
 </file>
@@ -57,23 +58,6 @@
       <c r="C1" t="inlineStr">
         <is>
           <t>Password</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>CONTOH123</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Contoh Nama (hapus baris ini)</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t/>
         </is>
       </c>
     </row>
@@ -137,4 +121,48 @@
     </row>
   </sheetData>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Tanggal</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>NIM</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Nama</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Judul</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>NamaFile</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>URL</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Waktu</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
 </file>